--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="107">
   <si>
     <t>ID</t>
   </si>
@@ -321,6 +326,33 @@
   </si>
   <si>
     <t>暗金70道士坐骑</t>
+  </si>
+  <si>
+    <t>粉色80战士坐骑</t>
+  </si>
+  <si>
+    <t>2003,2004,2007,2012,2001,31,32,2013,2010</t>
+  </si>
+  <si>
+    <t>80,80,80,80,80,80,80,80,80</t>
+  </si>
+  <si>
+    <t>粉色80法师坐骑</t>
+  </si>
+  <si>
+    <t>粉色80道士坐骑</t>
+  </si>
+  <si>
+    <t>粉色100战士坐骑</t>
+  </si>
+  <si>
+    <t>100,100,100,100,100,100,100,100,100,100</t>
+  </si>
+  <si>
+    <t>粉色100法师坐骑</t>
+  </si>
+  <si>
+    <t>粉色100道士坐骑</t>
   </si>
 </sst>
 </file>
@@ -333,7 +365,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -360,12 +392,6 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -837,137 +863,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -975,7 +1001,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1296,7 +1321,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1395,10 +1420,10 @@
       <c r="E6" s="4">
         <v>8205</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="5" t="s">
         <v>12</v>
       </c>
       <c r="H6" s="1">
@@ -1415,10 +1440,10 @@
       <c r="E7" s="4">
         <v>8205</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="5" t="s">
         <v>12</v>
       </c>
       <c r="H7" s="1">
@@ -1435,10 +1460,10 @@
       <c r="E8" s="4">
         <v>8205</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="5" t="s">
         <v>12</v>
       </c>
       <c r="H8" s="1">
@@ -1455,10 +1480,10 @@
       <c r="E9" s="4">
         <v>8205</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="5" t="s">
         <v>18</v>
       </c>
       <c r="H9" s="1">
@@ -1475,10 +1500,10 @@
       <c r="E10" s="4">
         <v>8205</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="5" t="s">
         <v>18</v>
       </c>
       <c r="H10" s="1">
@@ -1495,10 +1520,10 @@
       <c r="E11" s="4">
         <v>8205</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="5" t="s">
         <v>18</v>
       </c>
       <c r="H11" s="1">
@@ -1515,10 +1540,10 @@
       <c r="E12" s="1">
         <v>8206</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="5" t="s">
         <v>23</v>
       </c>
       <c r="H12" s="1">
@@ -1535,10 +1560,10 @@
       <c r="E13" s="1">
         <v>8206</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="5" t="s">
         <v>23</v>
       </c>
       <c r="H13" s="1">
@@ -1555,10 +1580,10 @@
       <c r="E14" s="1">
         <v>8206</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="5" t="s">
         <v>23</v>
       </c>
       <c r="H14" s="1">
@@ -1576,10 +1601,10 @@
       <c r="E16" s="1">
         <v>8206</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="5" t="s">
         <v>29</v>
       </c>
       <c r="H16" s="1">
@@ -1596,10 +1621,10 @@
       <c r="E17" s="1">
         <v>8206</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="5" t="s">
         <v>29</v>
       </c>
       <c r="H17" s="1">
@@ -1616,10 +1641,10 @@
       <c r="E18" s="1">
         <v>8206</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="5" t="s">
         <v>29</v>
       </c>
       <c r="H18" s="1">
@@ -1636,10 +1661,10 @@
       <c r="E19" s="1">
         <v>8207</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="5" t="s">
         <v>34</v>
       </c>
       <c r="H19" s="1">
@@ -1656,10 +1681,10 @@
       <c r="E20" s="1">
         <v>8207</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="5" t="s">
         <v>34</v>
       </c>
       <c r="H20" s="1">
@@ -1676,10 +1701,10 @@
       <c r="E21" s="1">
         <v>8207</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="5" t="s">
         <v>34</v>
       </c>
       <c r="H21" s="1">
@@ -1697,10 +1722,10 @@
       <c r="E23" s="1">
         <v>8207</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H23" s="1">
@@ -1717,10 +1742,10 @@
       <c r="E24" s="1">
         <v>8207</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H24" s="1">
@@ -1737,10 +1762,10 @@
       <c r="E25" s="1">
         <v>8207</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H25" s="1">
@@ -1757,10 +1782,10 @@
       <c r="E26" s="1">
         <v>8207</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H26" s="1">
@@ -1777,10 +1802,10 @@
       <c r="E27" s="1">
         <v>8207</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H27" s="1">
@@ -1797,10 +1822,10 @@
       <c r="E28" s="1">
         <v>8207</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H28" s="1">
@@ -1817,10 +1842,10 @@
       <c r="E29" s="1">
         <v>8207</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F29" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H29" s="1">
@@ -1837,10 +1862,10 @@
       <c r="E30" s="1">
         <v>8207</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="G30" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H30" s="1">
@@ -1857,10 +1882,10 @@
       <c r="E31" s="1">
         <v>8207</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="G31" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H31" s="1">
@@ -1877,10 +1902,10 @@
       <c r="E32" s="1">
         <v>8207</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="G32" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H32" s="1">
@@ -1897,10 +1922,10 @@
       <c r="E33" s="1">
         <v>8207</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="F33" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="G33" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H33" s="1">
@@ -1917,10 +1942,10 @@
       <c r="E34" s="1">
         <v>8207</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="F34" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="G34" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H34" s="1">
@@ -1938,10 +1963,10 @@
       <c r="E36" s="1">
         <v>8207</v>
       </c>
-      <c r="F36" s="6" t="s">
+      <c r="F36" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G36" s="6" t="s">
+      <c r="G36" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H36" s="1">
@@ -1958,10 +1983,10 @@
       <c r="E37" s="1">
         <v>8207</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="F37" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G37" s="6" t="s">
+      <c r="G37" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H37" s="1">
@@ -1978,10 +2003,10 @@
       <c r="E38" s="1">
         <v>8207</v>
       </c>
-      <c r="F38" s="6" t="s">
+      <c r="F38" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G38" s="6" t="s">
+      <c r="G38" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H38" s="1">
@@ -1998,10 +2023,10 @@
       <c r="E39" s="1">
         <v>8207</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G39" s="6" t="s">
+      <c r="G39" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H39" s="1">
@@ -2018,10 +2043,10 @@
       <c r="E40" s="1">
         <v>8207</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="F40" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="G40" s="6" t="s">
+      <c r="G40" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H40" s="1">
@@ -2038,10 +2063,10 @@
       <c r="E41" s="1">
         <v>8207</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="F41" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G41" s="6" t="s">
+      <c r="G41" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H41" s="1">
@@ -2058,10 +2083,10 @@
       <c r="E42" s="1">
         <v>8207</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="F42" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G42" s="6" t="s">
+      <c r="G42" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H42" s="1">
@@ -2078,10 +2103,10 @@
       <c r="E43" s="1">
         <v>8207</v>
       </c>
-      <c r="F43" s="6" t="s">
+      <c r="F43" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G43" s="6" t="s">
+      <c r="G43" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H43" s="1">
@@ -2098,10 +2123,10 @@
       <c r="E44" s="1">
         <v>8207</v>
       </c>
-      <c r="F44" s="6" t="s">
+      <c r="F44" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="G44" s="6" t="s">
+      <c r="G44" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H44" s="1">
@@ -2118,10 +2143,10 @@
       <c r="E45" s="1">
         <v>8207</v>
       </c>
-      <c r="F45" s="6" t="s">
+      <c r="F45" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="G45" s="6" t="s">
+      <c r="G45" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H45" s="1">
@@ -2138,10 +2163,10 @@
       <c r="E46" s="1">
         <v>8207</v>
       </c>
-      <c r="F46" s="6" t="s">
+      <c r="F46" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G46" s="6" t="s">
+      <c r="G46" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H46" s="1">
@@ -2158,10 +2183,10 @@
       <c r="E47" s="1">
         <v>8207</v>
       </c>
-      <c r="F47" s="6" t="s">
+      <c r="F47" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G47" s="6" t="s">
+      <c r="G47" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H47" s="1">
@@ -2179,10 +2204,10 @@
       <c r="E49" s="1">
         <v>8207</v>
       </c>
-      <c r="F49" s="6" t="s">
+      <c r="F49" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G49" s="6" t="s">
+      <c r="G49" s="5" t="s">
         <v>65</v>
       </c>
       <c r="H49" s="1">
@@ -2199,10 +2224,10 @@
       <c r="E50" s="1">
         <v>8207</v>
       </c>
-      <c r="F50" s="6" t="s">
+      <c r="F50" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G50" s="6" t="s">
+      <c r="G50" s="5" t="s">
         <v>65</v>
       </c>
       <c r="H50" s="1">
@@ -2219,10 +2244,10 @@
       <c r="E51" s="1">
         <v>8207</v>
       </c>
-      <c r="F51" s="6" t="s">
+      <c r="F51" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G51" s="6" t="s">
+      <c r="G51" s="5" t="s">
         <v>65</v>
       </c>
       <c r="H51" s="1">
@@ -2239,10 +2264,10 @@
       <c r="E52" s="1">
         <v>8207</v>
       </c>
-      <c r="F52" s="6" t="s">
+      <c r="F52" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G52" s="6" t="s">
+      <c r="G52" s="5" t="s">
         <v>65</v>
       </c>
       <c r="H52" s="1">
@@ -2259,10 +2284,10 @@
       <c r="E53" s="1">
         <v>8207</v>
       </c>
-      <c r="F53" s="6" t="s">
+      <c r="F53" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G53" s="6" t="s">
+      <c r="G53" s="5" t="s">
         <v>65</v>
       </c>
       <c r="H53" s="1">
@@ -2279,10 +2304,10 @@
       <c r="E54" s="1">
         <v>8207</v>
       </c>
-      <c r="F54" s="6" t="s">
+      <c r="F54" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="G54" s="6" t="s">
+      <c r="G54" s="5" t="s">
         <v>65</v>
       </c>
       <c r="H54" s="1">
@@ -2299,10 +2324,10 @@
       <c r="E55" s="1">
         <v>8207</v>
       </c>
-      <c r="F55" s="6" t="s">
+      <c r="F55" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G55" s="6" t="s">
+      <c r="G55" s="5" t="s">
         <v>65</v>
       </c>
       <c r="H55" s="1">
@@ -2319,10 +2344,10 @@
       <c r="E56" s="1">
         <v>8207</v>
       </c>
-      <c r="F56" s="6" t="s">
+      <c r="F56" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="G56" s="6" t="s">
+      <c r="G56" s="5" t="s">
         <v>65</v>
       </c>
       <c r="H56" s="1">
@@ -2339,10 +2364,10 @@
       <c r="E57" s="1">
         <v>8207</v>
       </c>
-      <c r="F57" s="6" t="s">
+      <c r="F57" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G57" s="6" t="s">
+      <c r="G57" s="5" t="s">
         <v>65</v>
       </c>
       <c r="H57" s="1">
@@ -2359,10 +2384,10 @@
       <c r="E58" s="1">
         <v>8207</v>
       </c>
-      <c r="F58" s="6" t="s">
+      <c r="F58" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="G58" s="6" t="s">
+      <c r="G58" s="5" t="s">
         <v>65</v>
       </c>
       <c r="H58" s="1">
@@ -2379,10 +2404,10 @@
       <c r="E59" s="1">
         <v>8207</v>
       </c>
-      <c r="F59" s="6" t="s">
+      <c r="F59" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G59" s="6" t="s">
+      <c r="G59" s="5" t="s">
         <v>65</v>
       </c>
       <c r="H59" s="1">
@@ -2399,10 +2424,10 @@
       <c r="E60" s="1">
         <v>8207</v>
       </c>
-      <c r="F60" s="6" t="s">
+      <c r="F60" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G60" s="6" t="s">
+      <c r="G60" s="5" t="s">
         <v>65</v>
       </c>
       <c r="H60" s="1">
@@ -2419,10 +2444,10 @@
       <c r="E61" s="1">
         <v>8207</v>
       </c>
-      <c r="F61" s="6" t="s">
+      <c r="F61" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="G61" s="6" t="s">
+      <c r="G61" s="5" t="s">
         <v>65</v>
       </c>
       <c r="H61" s="1">
@@ -2439,10 +2464,10 @@
       <c r="E62" s="1">
         <v>8207</v>
       </c>
-      <c r="F62" s="6" t="s">
+      <c r="F62" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="G62" s="6" t="s">
+      <c r="G62" s="5" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="1">
@@ -2459,10 +2484,10 @@
       <c r="E63" s="1">
         <v>8207</v>
       </c>
-      <c r="F63" s="6" t="s">
+      <c r="F63" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="G63" s="6" t="s">
+      <c r="G63" s="5" t="s">
         <v>65</v>
       </c>
       <c r="H63" s="1">
@@ -2479,10 +2504,10 @@
       <c r="E64" s="1">
         <v>8207</v>
       </c>
-      <c r="F64" s="6" t="s">
+      <c r="F64" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G64" s="6" t="s">
+      <c r="G64" s="5" t="s">
         <v>65</v>
       </c>
       <c r="H64" s="1">
@@ -2499,10 +2524,10 @@
       <c r="E65" s="1">
         <v>8207</v>
       </c>
-      <c r="F65" s="6" t="s">
+      <c r="F65" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G65" s="6" t="s">
+      <c r="G65" s="5" t="s">
         <v>65</v>
       </c>
       <c r="H65" s="1">
@@ -2519,10 +2544,10 @@
       <c r="E66" s="1">
         <v>8207</v>
       </c>
-      <c r="F66" s="6" t="s">
+      <c r="F66" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G66" s="6" t="s">
+      <c r="G66" s="5" t="s">
         <v>65</v>
       </c>
       <c r="H66" s="1">
@@ -2539,10 +2564,10 @@
       <c r="E67" s="1">
         <v>8207</v>
       </c>
-      <c r="F67" s="6" t="s">
+      <c r="F67" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="G67" s="6" t="s">
+      <c r="G67" s="5" t="s">
         <v>65</v>
       </c>
       <c r="H67" s="1">
@@ -2559,10 +2584,10 @@
       <c r="E68" s="1">
         <v>8207</v>
       </c>
-      <c r="F68" s="6" t="s">
+      <c r="F68" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="G68" s="6" t="s">
+      <c r="G68" s="5" t="s">
         <v>65</v>
       </c>
       <c r="H68" s="1">
@@ -2579,10 +2604,10 @@
       <c r="E69" s="1">
         <v>8207</v>
       </c>
-      <c r="F69" s="6" t="s">
+      <c r="F69" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="G69" s="6" t="s">
+      <c r="G69" s="5" t="s">
         <v>65</v>
       </c>
       <c r="H69" s="1">
@@ -2599,10 +2624,10 @@
       <c r="E71" s="1">
         <v>8209</v>
       </c>
-      <c r="F71" s="6" t="s">
+      <c r="F71" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="G71" s="6" t="s">
+      <c r="G71" s="5" t="s">
         <v>73</v>
       </c>
       <c r="H71" s="1">
@@ -2619,10 +2644,10 @@
       <c r="E72" s="1">
         <v>8209</v>
       </c>
-      <c r="F72" s="6" t="s">
+      <c r="F72" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="G72" s="6" t="s">
+      <c r="G72" s="5" t="s">
         <v>73</v>
       </c>
       <c r="H72" s="1">
@@ -2639,10 +2664,10 @@
       <c r="E73" s="1">
         <v>8209</v>
       </c>
-      <c r="F73" s="6" t="s">
+      <c r="F73" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="G73" s="6" t="s">
+      <c r="G73" s="5" t="s">
         <v>73</v>
       </c>
       <c r="H73" s="1">
@@ -2659,10 +2684,10 @@
       <c r="E75" s="1">
         <v>8209</v>
       </c>
-      <c r="F75" s="6" t="s">
+      <c r="F75" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="G75" s="6" t="s">
+      <c r="G75" s="5" t="s">
         <v>79</v>
       </c>
       <c r="H75" s="1">
@@ -2679,10 +2704,10 @@
       <c r="E76" s="1">
         <v>8209</v>
       </c>
-      <c r="F76" s="6" t="s">
+      <c r="F76" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="G76" s="6" t="s">
+      <c r="G76" s="5" t="s">
         <v>79</v>
       </c>
       <c r="H76" s="1">
@@ -2699,10 +2724,10 @@
       <c r="E77" s="1">
         <v>8209</v>
       </c>
-      <c r="F77" s="6" t="s">
+      <c r="F77" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="G77" s="6" t="s">
+      <c r="G77" s="5" t="s">
         <v>79</v>
       </c>
       <c r="H77" s="1">
@@ -2719,10 +2744,10 @@
       <c r="E80" s="1">
         <v>8308</v>
       </c>
-      <c r="F80" s="6" t="s">
+      <c r="F80" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="G80" s="6" t="s">
+      <c r="G80" s="5" t="s">
         <v>84</v>
       </c>
       <c r="H80" s="1">
@@ -2739,10 +2764,10 @@
       <c r="E81" s="1">
         <v>8308</v>
       </c>
-      <c r="F81" s="6" t="s">
+      <c r="F81" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="G81" s="6" t="s">
+      <c r="G81" s="5" t="s">
         <v>84</v>
       </c>
       <c r="H81" s="1">
@@ -2759,10 +2784,10 @@
       <c r="E82" s="1">
         <v>8308</v>
       </c>
-      <c r="F82" s="6" t="s">
+      <c r="F82" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="G82" s="6" t="s">
+      <c r="G82" s="5" t="s">
         <v>84</v>
       </c>
       <c r="H82" s="1">
@@ -2779,10 +2804,10 @@
       <c r="E84" s="1">
         <v>8308</v>
       </c>
-      <c r="F84" s="6" t="s">
+      <c r="F84" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="G84" s="6" t="s">
+      <c r="G84" s="5" t="s">
         <v>73</v>
       </c>
       <c r="H84" s="1">
@@ -2799,10 +2824,10 @@
       <c r="E85" s="1">
         <v>8308</v>
       </c>
-      <c r="F85" s="6" t="s">
+      <c r="F85" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="G85" s="6" t="s">
+      <c r="G85" s="5" t="s">
         <v>73</v>
       </c>
       <c r="H85" s="1">
@@ -2819,10 +2844,10 @@
       <c r="E86" s="1">
         <v>8308</v>
       </c>
-      <c r="F86" s="6" t="s">
+      <c r="F86" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="G86" s="6" t="s">
+      <c r="G86" s="5" t="s">
         <v>73</v>
       </c>
       <c r="H86" s="1">
@@ -2839,10 +2864,10 @@
       <c r="E87" s="1">
         <v>8308</v>
       </c>
-      <c r="F87" s="6" t="s">
+      <c r="F87" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="G87" s="6" t="s">
+      <c r="G87" s="5" t="s">
         <v>79</v>
       </c>
       <c r="H87" s="1">
@@ -2859,10 +2884,10 @@
       <c r="E88" s="1">
         <v>8308</v>
       </c>
-      <c r="F88" s="6" t="s">
+      <c r="F88" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="G88" s="6" t="s">
+      <c r="G88" s="5" t="s">
         <v>79</v>
       </c>
       <c r="H88" s="1">
@@ -2879,33 +2904,135 @@
       <c r="E89" s="1">
         <v>8308</v>
       </c>
-      <c r="F89" s="6" t="s">
+      <c r="F89" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="G89" s="6" t="s">
+      <c r="G89" s="5" t="s">
         <v>79</v>
       </c>
       <c r="H89" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="90" customHeight="1" spans="3:8">
-      <c r="F90" s="5"/>
-    </row>
     <row r="91" customHeight="1" spans="3:8">
-      <c r="F91" s="5"/>
+      <c r="C91" s="1">
+        <v>921</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E91" s="1">
+        <v>8308</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="H91" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="92" customHeight="1" spans="3:8">
-      <c r="F92" s="5"/>
+      <c r="C92" s="1">
+        <v>922</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E92" s="1">
+        <v>8308</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="H92" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="93" customHeight="1" spans="3:8">
-      <c r="F93" s="5"/>
+      <c r="C93" s="1">
+        <v>923</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E93" s="1">
+        <v>8308</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="H93" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="94" customHeight="1" spans="3:8">
-      <c r="F94" s="5"/>
+      <c r="C94" s="1">
+        <v>924</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E94" s="1">
+        <v>8308</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="H94" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="95" customHeight="1" spans="3:8">
-      <c r="F95" s="5"/>
+      <c r="C95" s="1">
+        <v>925</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E95" s="1">
+        <v>8308</v>
+      </c>
+      <c r="F95" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="H95" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="3:8">
+      <c r="C96" s="1">
+        <v>926</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E96" s="1">
+        <v>8308</v>
+      </c>
+      <c r="F96" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="H96" s="1">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="109">
   <si>
     <t>ID</t>
   </si>
@@ -340,7 +340,13 @@
     <t>粉色80法师坐骑</t>
   </si>
   <si>
+    <t>2003,2005,2008,2012,2001,31,32,2013,2010</t>
+  </si>
+  <si>
     <t>粉色80道士坐骑</t>
+  </si>
+  <si>
+    <t>2003,2006,2009,2012,2001,31,32,2013,2010</t>
   </si>
   <si>
     <t>粉色100战士坐骑</t>
@@ -2922,7 +2928,7 @@
         <v>98</v>
       </c>
       <c r="E91" s="1">
-        <v>8308</v>
+        <v>8309</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>99</v>
@@ -2942,10 +2948,10 @@
         <v>101</v>
       </c>
       <c r="E92" s="1">
-        <v>8308</v>
+        <v>8309</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G92" s="5" t="s">
         <v>100</v>
@@ -2959,13 +2965,13 @@
         <v>923</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E93" s="1">
-        <v>8308</v>
+        <v>8309</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G93" s="5" t="s">
         <v>100</v>
@@ -2979,16 +2985,16 @@
         <v>924</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E94" s="1">
-        <v>8308</v>
+        <v>8309</v>
       </c>
       <c r="F94" s="5" t="s">
         <v>99</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H94" s="1">
         <v>1</v>
@@ -2999,16 +3005,16 @@
         <v>925</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E95" s="1">
-        <v>8308</v>
+        <v>8309</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H95" s="1">
         <v>2</v>
@@ -3019,16 +3025,16 @@
         <v>926</v>
       </c>
       <c r="D96" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E96" s="1">
+        <v>8309</v>
+      </c>
+      <c r="F96" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G96" s="5" t="s">
         <v>106</v>
-      </c>
-      <c r="E96" s="1">
-        <v>8308</v>
-      </c>
-      <c r="F96" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="G96" s="5" t="s">
-        <v>104</v>
       </c>
       <c r="H96" s="1">
         <v>3</v>
